--- a/nrl_match_stats_specific_urls.xlsx
+++ b/nrl_match_stats_specific_urls.xlsx
@@ -588,22 +588,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TITANS</t>
+          <t>TIGERS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -613,77 +613,77 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>169</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>29/36</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>38/40</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>319</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>419</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -723,44 +723,44 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PANTHERS</t>
+          <t>DOLPHINS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -785,112 +785,112 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>491</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>29/36</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>31/39</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
